--- a/Raw Data/Projects and PCH.xlsx
+++ b/Raw Data/Projects and PCH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2650736-72C0-438A-9774-5FB34DF5B1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4962EC-DE2F-4859-BF63-44B134DC520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>Mr. Sanjay Kumar Gupta</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>TA509</t>
+  </si>
+  <si>
+    <t>TA601</t>
+  </si>
+  <si>
+    <t>TB501</t>
   </si>
 </sst>
 </file>
@@ -655,11 +661,23 @@
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>

--- a/Raw Data/Projects and PCH.xlsx
+++ b/Raw Data/Projects and PCH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4962EC-DE2F-4859-BF63-44B134DC520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21697C3-D18A-4A76-BD5C-D473CE37065F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>Mr. Sanjay Kumar Gupta</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>TB501</t>
+  </si>
+  <si>
+    <t>Mr. Nabajit Baruah</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -574,7 +577,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -585,7 +588,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>

--- a/Raw Data/Projects and PCH.xlsx
+++ b/Raw Data/Projects and PCH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21697C3-D18A-4A76-BD5C-D473CE37065F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF3DF6B-18E6-42A2-AB03-FDA5871BC008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
   <si>
     <t>Mr. Sanjay Kumar Gupta</t>
   </si>
@@ -114,13 +114,25 @@
   </si>
   <si>
     <t>Mr. Nabajit Baruah</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Guj/Kar/MP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,16 +156,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFCFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -161,11 +183,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2EC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -181,6 +218,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,6 +521,9 @@
       <c r="C1" t="s">
         <v>17</v>
       </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -486,6 +532,10 @@
       <c r="B2" t="s">
         <v>1</v>
       </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -494,8 +544,11 @@
       <c r="B3" t="s">
         <v>2</v>
       </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="7"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -505,8 +558,11 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="H4" s="6"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -516,8 +572,11 @@
       <c r="B5" t="s">
         <v>4</v>
       </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="H5" s="7"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -527,8 +586,11 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="6"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -538,8 +600,11 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -549,8 +614,11 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="6"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -560,8 +628,11 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="7"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -571,8 +642,11 @@
       <c r="B10" t="s">
         <v>10</v>
       </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="6"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -582,8 +656,11 @@
       <c r="B11" t="s">
         <v>11</v>
       </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -593,8 +670,11 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -604,8 +684,11 @@
       <c r="B13" t="s">
         <v>19</v>
       </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="7"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -615,8 +698,11 @@
       <c r="B14" t="s">
         <v>13</v>
       </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="6"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -626,8 +712,11 @@
       <c r="B15" t="s">
         <v>14</v>
       </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -637,8 +726,11 @@
       <c r="B16" t="s">
         <v>20</v>
       </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="6"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -648,8 +740,11 @@
       <c r="B17" t="s">
         <v>21</v>
       </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="7"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -659,8 +754,11 @@
       <c r="B18" t="s">
         <v>22</v>
       </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
       <c r="G18" s="3"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="7"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -670,29 +768,34 @@
       <c r="B19" t="s">
         <v>23</v>
       </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="H19" s="6"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
       </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="G21" s="3"/>
-      <c r="H21" s="2"/>
+      <c r="H21" s="6"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">

--- a/Raw Data/Projects and PCH.xlsx
+++ b/Raw Data/Projects and PCH.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF3DF6B-18E6-42A2-AB03-FDA5871BC008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFF9298-8F93-4FBA-A427-01A2A19156BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>Mr. Sanjay Kumar Gupta</t>
   </si>
@@ -125,7 +128,13 @@
     <t>North</t>
   </si>
   <si>
-    <t>Guj/Kar/MP</t>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>Guj/Kar</t>
+  </si>
+  <si>
+    <t>TA310</t>
   </si>
 </sst>
 </file>
@@ -587,7 +596,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="6"/>
@@ -615,7 +624,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="6"/>
@@ -629,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="7"/>
@@ -699,7 +708,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="6"/>
@@ -769,7 +778,7 @@
         <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="6"/>
@@ -790,6 +799,15 @@
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
       <c r="G21" s="3"/>
       <c r="H21" s="6"/>
       <c r="I21" s="2"/>

--- a/Raw Data/Projects and PCH.xlsx
+++ b/Raw Data/Projects and PCH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFF9298-8F93-4FBA-A427-01A2A19156BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8685DFE4-3928-421D-A612-A0FDBFED415D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
-  <si>
-    <t>Mr. Sanjay Kumar Gupta</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
   <si>
     <t>TA413</t>
   </si>
@@ -95,9 +92,6 @@
     <t>Project Name</t>
   </si>
   <si>
-    <t>Mr. Dheeraj Vashishth</t>
-  </si>
-  <si>
     <t>TA513</t>
   </si>
   <si>
@@ -135,6 +129,9 @@
   </si>
   <si>
     <t>TA310</t>
+  </si>
+  <si>
+    <t>Mr. NK Gupta</t>
   </si>
 </sst>
 </file>
@@ -169,6 +166,7 @@
       <sz val="11"/>
       <color rgb="FF111827"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -522,39 +520,39 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="7"/>
@@ -562,13 +560,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="6"/>
@@ -576,13 +574,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="7"/>
@@ -590,13 +588,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="6"/>
@@ -604,13 +602,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="7"/>
@@ -618,13 +616,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="6"/>
@@ -632,13 +630,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="7"/>
@@ -646,13 +644,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="6"/>
@@ -660,13 +658,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="7"/>
@@ -674,13 +672,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="6"/>
@@ -688,13 +686,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="7"/>
@@ -702,13 +700,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="6"/>
@@ -716,13 +714,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="7"/>
@@ -730,13 +728,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="6"/>
@@ -744,13 +742,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="7"/>
@@ -758,13 +756,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="7"/>
@@ -772,13 +770,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="6"/>
@@ -786,13 +784,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="7"/>
@@ -800,13 +798,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="6"/>

--- a/Raw Data/Projects and PCH.xlsx
+++ b/Raw Data/Projects and PCH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8685DFE4-3928-421D-A612-A0FDBFED415D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20FE75E-C3E4-4765-948C-8A2BE3DF8FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
   <si>
     <t>TA413</t>
   </si>
@@ -132,6 +132,30 @@
   </si>
   <si>
     <t>Mr. NK Gupta</t>
+  </si>
+  <si>
+    <t>TA510</t>
+  </si>
+  <si>
+    <t>TB608</t>
+  </si>
+  <si>
+    <t>TA602</t>
+  </si>
+  <si>
+    <t>NER</t>
+  </si>
+  <si>
+    <t>TB 501 - 132kV</t>
+  </si>
+  <si>
+    <t>TB 501 - 220kV</t>
+  </si>
+  <si>
+    <t>TB 507 - 400kV</t>
+  </si>
+  <si>
+    <t>TB 507 - 765kV</t>
   </si>
 </sst>
 </file>
@@ -811,35 +835,98 @@
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
       <c r="G22" s="2"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>

--- a/Raw Data/Projects and PCH.xlsx
+++ b/Raw Data/Projects and PCH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20FE75E-C3E4-4765-948C-8A2BE3DF8FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D3FA04-6011-443A-9167-82690A733330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="40">
   <si>
     <t>TA413</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>TB 507 - 765kV</t>
+  </si>
+  <si>
+    <t>TA515</t>
   </si>
 </sst>
 </file>
@@ -932,6 +935,15 @@
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
